--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73492559</v>
+        <v>73485199</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>786</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,13 +712,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553438.0503849548</v>
+        <v>553300</v>
       </c>
       <c r="R2" t="n">
-        <v>6557360.955430424</v>
+        <v>6557605</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,19 +745,9 @@
           <t>2018-10-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +767,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Grandominerad gallringsskog</t>
+          <t>Grandominerad skog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73492522</v>
+        <v>73486964</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,38 +796,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kalkbrottsvillorna, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553248.694256213</v>
+        <v>553512</v>
       </c>
       <c r="R3" t="n">
-        <v>6557599.403948564</v>
+        <v>6557367</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +855,9 @@
           <t>2018-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +877,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Grandominerad gallringsskog</t>
+          <t>Barrblandskog skog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73492516</v>
+        <v>73593981</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,38 +906,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kalkbrottsvillorna, Srm</t>
+          <t>Kalkbrottsvillorna mot sjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553192.1940020721</v>
+        <v>552990</v>
       </c>
       <c r="R4" t="n">
-        <v>6557634.522512906</v>
+        <v>6557738</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1001,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +987,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Grandominerad gallringsskog</t>
+          <t>Lövblandskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,37 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73492488</v>
+        <v>73485193</v>
       </c>
       <c r="B5" t="n">
-        <v>86134</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4377</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blodvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553166.8192763308</v>
+        <v>553300</v>
       </c>
       <c r="R5" t="n">
-        <v>6557685.463268213</v>
+        <v>6557605</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,19 +1075,9 @@
           <t>2018-10-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Grandominerad gallringsskog</t>
+          <t>Grandominerad skog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1176,6 +1112,1449 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73492488</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>553167</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6557685</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Grandominerad gallringsskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>73492559</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>553438</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6557361</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Grandominerad gallringsskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>73486082</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>553367</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6557532</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog skog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122066819</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hjälmarsvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>553006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557744</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>86735493</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fjolårsunge</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>214, Vingåker, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>552985</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6557719</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>85753022</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>553557</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6557293</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Lidén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Lidén, Ylva Linnman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>73485197</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>553300</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6557605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad skog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>73486968</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>553512</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6557367</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrblandskog skog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73492390</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>553475</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6557406</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrblandskog,</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>73492404</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>553417</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6557467</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrblandskog,</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73593983</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna mot sjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>552990</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557738</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2018-10-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2018-10-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövblandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73492516</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>553192</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557635</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Grandominerad gallringsskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>73492522</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kalkbrottsvillorna, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>553249</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557599</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vingåker</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-10-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Grandominerad gallringsskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54381-2023 artfynd.xlsx
+++ b/artfynd/A 54381-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73485199</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73486964</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73593981</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73485193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492559</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73486082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122066819</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86735493</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85753022</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73485197</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1995,6 +2055,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73486968</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492390</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2219,6 +2289,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492404</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2331,6 +2406,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73593983</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2443,6 +2523,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492516</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2555,8 +2640,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73492522</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>